--- a/Assets/ConfigTables/XLSX/C_测试导表.xlsx
+++ b/Assets/ConfigTables/XLSX/C_测试导表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyUnityProjects\GameFramework\Assets\ConfigTables\XLSX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FE6DB59-ED4D-4277-A3F2-4ADFE332D7ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06D2A5F4-659A-471C-917C-814FA381863A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="723" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1970" yWindow="1700" windowWidth="28800" windowHeight="15370" tabRatio="723" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TestOneData" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="51">
   <si>
     <t>int</t>
   </si>
@@ -87,14 +87,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>1.1f</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1f</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>bool</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -185,10 +177,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>1f,2.0f,3.3f</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>TRUE,FALSE</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -197,10 +185,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>FALSE,FALSE,FALSE,FALSE</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>FALSE,FALSE,FALSE</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -241,7 +225,12 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>UI_SideBarEntry</t>
+    <t>NonEmpty,Unique</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,2.0,3.3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -644,7 +633,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="10.58203125" customWidth="1"/>
@@ -656,19 +645,19 @@
         <v>2</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>12</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:6" s="7" customFormat="1" ht="32" customHeight="1">
@@ -685,10 +674,10 @@
         <v>11</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:6" s="7" customFormat="1" ht="32" customHeight="1">
@@ -696,27 +685,27 @@
         <v>4</v>
       </c>
       <c r="B3" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>19</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>21</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>13</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:6" s="7" customFormat="1" ht="32" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
@@ -734,12 +723,12 @@
         <v>1</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B6" s="1">
         <v>10001</v>
@@ -747,8 +736,8 @@
       <c r="C6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>15</v>
+      <c r="D6" s="1">
+        <v>1</v>
       </c>
       <c r="E6" s="2" t="b">
         <v>1</v>
@@ -759,7 +748,7 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B7" s="1">
         <v>10002</v>
@@ -767,8 +756,8 @@
       <c r="C7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>14</v>
+      <c r="D7" s="1">
+        <v>1.1000000000000001</v>
       </c>
       <c r="E7" s="2" t="b">
         <v>0</v>
@@ -779,7 +768,7 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B8" s="1">
         <v>10003</v>
@@ -791,13 +780,11 @@
       <c r="E8" s="2"/>
       <c r="F8" s="1"/>
     </row>
+    <row r="9" spans="1:6">
+      <c r="B9" s="1"/>
+    </row>
     <row r="23" spans="4:4">
       <c r="D23" s="9"/>
-    </row>
-    <row r="37" spans="6:6">
-      <c r="F37" t="s">
-        <v>53</v>
-      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -819,19 +806,19 @@
         <v>2</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>35</v>
-      </c>
       <c r="F1" s="4" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:6" s="7" customFormat="1" ht="32" customHeight="1">
@@ -842,16 +829,16 @@
         <v>0</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>36</v>
-      </c>
       <c r="F2" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:6" s="7" customFormat="1" ht="32" customHeight="1">
@@ -859,27 +846,27 @@
         <v>4</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E3" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>47</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:6" s="7" customFormat="1" ht="32" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:6" s="7" customFormat="1" ht="15" customHeight="1">
@@ -888,57 +875,55 @@
       </c>
       <c r="B5" s="10"/>
       <c r="C5" s="4" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B6" s="1">
         <v>10001</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="E6" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B7" s="1">
         <v>10002</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B8" s="1">
         <v>10003</v>
       </c>
       <c r="C8" s="9"/>
-      <c r="E8" s="9" t="s">
-        <v>42</v>
-      </c>
+      <c r="E8" s="9"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
